--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T12:02:06+00:00</t>
+    <t>2026-07-20T15:05:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -474,18 +474,10 @@
 </t>
   </si>
   <si>
-    <t>CarePlan Custodian (Extension)</t>
-  </si>
-  <si>
-    <t>Verantwortliche Stelle für Pflege und Aktualisierung des Versorgungsplans (Custodian).
-Übernahme der **MCC eCare Plan** Extension
-[custodian](https://build.fhir.org/ig/HL7/fhir-us-mcc/StructureDefinition-custodian.html)
-(`http://hl7.org/fhir/us/mcc/StructureDefinition/custodian`). Es handelt sich um einen
-R5-Backport: In FHIR R5 wurde `CarePlan.author` entfernt; `CarePlan.custodian` benennt die
-für Pflege und Wartung des Plans verantwortliche Partei. Der Custodian kann, muss aber kein
-Contributor sein.
-Hier als lokale Extension nachgebildet, um die US-Realm-Abhängigkeit (US MCC / US Core) zu
-vermeiden; Wertebereich an die Referenztypen der MCC-Extension angelehnt.</t>
+    <t>Custodian</t>
+  </si>
+  <si>
+    <t>Für Pflege und Aktualisierung des Diagnostik-Plans verantwortliche Stelle – R5-Backport aus MCC.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -640,10 +632,7 @@
     <t>CarePlan.status</t>
   </si>
   <si>
-    <t>draft | active | on-hold | revoked | completed | entered-in-error | unknown</t>
-  </si>
-  <si>
-    <t>Indicates whether the plan is currently being acted upon, represents future intentions or is now a historical record.</t>
+    <t>Status des Diagnostik-Plans – z. B. active, completed.</t>
   </si>
   <si>
     <t>The unknown code is not to be used to convey other statuses.  The unknown code should be used when one of the statuses applies, but the authoring system doesn't know the current state of the care plan.
@@ -656,6 +645,9 @@
     <t>required</t>
   </si>
   <si>
+    <t>Indicates whether the plan is currently being acted upon, represents future intentions or is now a historical record.</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/request-status|4.0.1</t>
   </si>
   <si>
@@ -702,10 +694,10 @@
 </t>
   </si>
   <si>
-    <t>Type of plan</t>
-  </si>
-  <si>
-    <t>Identifies what "kind" of plan this is to support differentiation between multiple co-existing plans; e.g. "Home health", "psychiatric", "asthma", "disease management", "wellness plan", etc.</t>
+    <t>Plan-Kategorie</t>
+  </si>
+  <si>
+    <t>Kennzeichnung des Plan-Typs; category.text trägt verpflichtend den Wert Tumordiagnostik.</t>
   </si>
   <si>
     <t>There may be multiple axes of categorization and one plan may serve multiple purposes.  In some cases, this may be redundant with references to CarePlan.concern.</t>
@@ -850,10 +842,10 @@
 </t>
   </si>
   <si>
-    <t>Who the care plan is for</t>
-  </si>
-  <si>
-    <t>Identifies the patient or group whose intended care is described by the plan.</t>
+    <t>Patientin/Patient</t>
+  </si>
+  <si>
+    <t>Person, für die die Diagnostik durchgeführt wird.</t>
   </si>
   <si>
     <t>Request.subject</t>
@@ -907,10 +899,10 @@
 </t>
   </si>
   <si>
-    <t>Time period plan covers</t>
-  </si>
-  <si>
-    <t>Indicates when the plan did (or is intended to) come into effect and end.</t>
+    <t>Diagnostikzeitraum</t>
+  </si>
+  <si>
+    <t>Zeitraum der Diagnostikphase von Beginn bis Diagnosesicherung.</t>
   </si>
   <si>
     <t>Any activities scheduled as part of the plan should be constrained to the specified period regardless of whether the activities are planned within a single encounter/episode or across multiple encounters/episodes (e.g. the longitudinal management of a chronic condition).</t>
@@ -982,10 +974,10 @@
     <t>CarePlan.contributor</t>
   </si>
   <si>
-    <t>Who provided the content of the care plan</t>
-  </si>
-  <si>
-    <t>Identifies the individual(s) or organization who provided the contents of the care plan.</t>
+    <t>Beteiligte</t>
+  </si>
+  <si>
+    <t>Personen oder Organisationen, die zur Diagnostik beigetragen haben.</t>
   </si>
   <si>
     <t>Collaborative care plans may have multiple contributors.</t>
@@ -998,10 +990,10 @@
 </t>
   </si>
   <si>
-    <t>Who's involved in plan?</t>
-  </si>
-  <si>
-    <t>Identifies all people and organizations who are expected to be involved in the care envisioned by this plan.</t>
+    <t>Behandlungsteam</t>
+  </si>
+  <si>
+    <t>An der Diagnostik beteiligtes Versorgungsteam.</t>
   </si>
   <si>
     <t>Allows representation of care teams, helps scope care plan.  In some cases may be a determiner of access permissions.</t>
@@ -1051,10 +1043,10 @@
 </t>
   </si>
   <si>
-    <t>Information considered as part of plan</t>
-  </si>
-  <si>
-    <t>Identifies portions of the patient's record that specifically influenced the formation of the plan.  These might include comorbidities, recent procedures, limitations, recent assessments, etc.</t>
+    <t>Ergänzende Information</t>
+  </si>
+  <si>
+    <t>Ergänzende Informationen zum Diagnostik-Plan.</t>
   </si>
   <si>
     <t>Use "concern" to identify specific conditions addressed by the care plan.</t>
@@ -1098,10 +1090,10 @@
 </t>
   </si>
   <si>
-    <t>Action to occur as part of plan</t>
-  </si>
-  <si>
-    <t>Identifies a planned action to occur as part of the plan.  For example, a medication to be used, lab tests to perform, self-monitoring, education, etc.</t>
+    <t>Diagnostische Maßnahmen</t>
+  </si>
+  <si>
+    <t>Geplante bzw. durchgeführte Schritte des Diagnosepfads.</t>
   </si>
   <si>
     <t>Allows systems to prompt for performance of planned activities, and validate plans against best practice.</t>
@@ -1166,10 +1158,10 @@
 </t>
   </si>
   <si>
-    <t>Appointment, Encounter, Procedure, etc.</t>
-  </si>
-  <si>
-    <t>Details of the outcome or action resulting from the activity.  The reference to an "event" resource, such as Procedure or Encounter or Observation, is the result/outcome of the activity itself.  The activity can be conveyed using CarePlan.activity.detail OR using the CarePlan.activity.reference (a reference to a “request” resource).</t>
+    <t>Ergebnis</t>
+  </si>
+  <si>
+    <t>Referenz auf das Ergebnis der Diagnostik – z. B. DiagnosticReport oder Observation.</t>
   </si>
   <si>
     <t>The activity outcome is independent of the outcome of the related goal(s).  For example, if the goal is to achieve a target body weight of 150 lbs and an activity is defined to diet, then the activity outcome could be calories consumed whereas the goal outcome is an observation for the actual body weight measured.</t>
@@ -1216,10 +1208,10 @@
 </t>
   </si>
   <si>
-    <t>Activity details defined in specific resource</t>
-  </si>
-  <si>
-    <t>The details of the proposed activity represented in a specific resource.</t>
+    <t>Geplante Maßnahme</t>
+  </si>
+  <si>
+    <t>Referenz auf eine geplante diagnostische Maßnahme – z. B. ServiceRequest.</t>
   </si>
   <si>
     <t>Standard extension exists ([resource-pertainsToGoal](http://hl7.org/fhir/R4/extension-resource-pertainstogoal.html)) that allows goals to be referenced from any of the referenced resources in CarePlan.activity.reference.  @@ -3946,16 +3938,16 @@
         <v>108</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -3980,10 +3972,10 @@
         <v>80</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Y18" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="Z18" t="s" s="2">
         <v>198</v>
@@ -4096,7 +4088,7 @@
         <v>80</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Y19" t="s" s="2">
         <v>208</v>
@@ -7528,7 +7520,7 @@
         <v>80</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Y49" t="s" s="2">
         <v>395</v>
@@ -8332,7 +8324,7 @@
         <v>80</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Y56" t="s" s="2">
         <v>435</v>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T15:05:40+00:00</t>
+    <t>2026-07-27T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:55:12+00:00</t>
+    <t>2026-07-28T00:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:29:57+00:00</t>
+    <t>2026-07-28T09:41:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T09:41:52+00:00</t>
+    <t>2026-07-29T10:30:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T10:30:12+00:00</t>
+    <t>2026-07-29T11:12:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:12:20+00:00</t>
+    <t>2026-07-29T12:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:36:35+00:00</t>
+    <t>2026-07-30T15:22:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:22:14+00:00</t>
+    <t>2026-07-31T08:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:51:02+00:00</t>
+    <t>2026-07-31T12:16:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="507">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:16:37+00:00</t>
+    <t>2026-07-31T12:21:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -666,10 +666,10 @@
     <t>CarePlan.intent</t>
   </si>
   <si>
-    <t>proposal | plan | order | option</t>
-  </si>
-  <si>
-    <t>Indicates the level of authority/intentionality associated with the care plan and where the care plan fits into the workflow chain.</t>
+    <t>Planart</t>
+  </si>
+  <si>
+    <t>Art des Plans – typischerweise plan für den Diagnostikplan.</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
@@ -1061,305 +1061,309 @@
     <t>CarePlan.goal</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/onko-therapy-goal)
+</t>
+  </si>
+  <si>
+    <t>Diagnoseziel</t>
+  </si>
+  <si>
+    <t>Ziel des Diagnostikplans – z. B. Diagnosesicherung mit Staging und Rezeptorstatus.</t>
+  </si>
+  <si>
+    <t>Goal can be achieving a particular change or merely maintaining a current state or even slowing a decline.</t>
+  </si>
+  <si>
+    <t>Provides context for plan.  Allows plan effectiveness to be evaluated by clinicians.</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode&lt;=OBJ].</t>
+  </si>
+  <si>
+    <t>GOL.1</t>
+  </si>
+  <si>
+    <t>CarePlan.activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Diagnostische Maßnahmen</t>
+  </si>
+  <si>
+    <t>Geplante bzw. durchgeführte Schritte des Diagnosepfads.</t>
+  </si>
+  <si>
+    <t>Allows systems to prompt for performance of planned activities, and validate plans against best practice.</t>
+  </si>
+  <si>
+    <t>cpl-3:Provide a reference or detail, not both {detail.empty() or reference.empty()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
+    <t>{no mapping
+NOTE: This is a list of contained Request-Event tuples!}</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP].target</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.id</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.outcomeCodeableConcept</t>
+  </si>
+  <si>
+    <t>Results of the activity</t>
+  </si>
+  <si>
+    <t>Identifies the outcome at the point when the status of the activity is assessed.  For example, the outcome of an education activity could be patient understands (or not).</t>
+  </si>
+  <si>
+    <t>Note that this should not duplicate the activity status (e.g. completed or in progress).</t>
+  </si>
+  <si>
+    <t>Identifies the results of the activity.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome|4.0.1</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.outcomeReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(DiagnosticReport|Observation|Procedure)
+</t>
+  </si>
+  <si>
+    <t>Ergebnis</t>
+  </si>
+  <si>
+    <t>Referenz auf das Ergebnis der Diagnostik – z. B. DiagnosticReport oder Observation.</t>
+  </si>
+  <si>
+    <t>The activity outcome is independent of the outcome of the related goal(s).  For example, if the goal is to achieve a target body weight of 150 lbs and an activity is defined to diet, then the activity outcome could be calories consumed whereas the goal outcome is an observation for the actual body weight measured.</t>
+  </si>
+  <si>
+    <t>Links plan to resulting actions.</t>
+  </si>
+  <si>
+    <t>{Event that is outcome of Request in activity.reference}</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=FLFS].source</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annotation
+</t>
+  </si>
+  <si>
+    <t>Comments about the activity status/progress</t>
+  </si>
+  <si>
+    <t>Notes about the adherence/status/progress of the activity.</t>
+  </si>
+  <si>
+    <t>This element should NOT be used to describe the activity to be performed - that occurs either within the resource pointed to by activity.detail.reference or in activity.detail.description.</t>
+  </si>
+  <si>
+    <t>Can be used to capture information about adherence, progress, concerns, etc.</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="annotation"].value</t>
+  </si>
+  <si>
+    <t>NTE?</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(ServiceRequest|Appointment|Task)
+</t>
+  </si>
+  <si>
+    <t>Geplante Maßnahme</t>
+  </si>
+  <si>
+    <t>Referenz auf eine geplante diagnostische Maßnahme – z. B. ServiceRequest.</t>
+  </si>
+  <si>
+    <t>Standard extension exists ([resource-pertainsToGoal](http://hl7.org/fhir/R4/extension-resource-pertainstogoal.html)) that allows goals to be referenced from any of the referenced resources in CarePlan.activity.reference.  +The goal should be visible when the resource referenced by CarePlan.activity.reference is viewed independently from the CarePlan.  Requests that are pointed to by a CarePlan using this element should *not* point to this CarePlan using the "basedOn" element.  i.e. Requests that are part of a CarePlan are not "based on" the CarePlan.</t>
+  </si>
+  <si>
+    <t>Details in a form consistent with other applications and contexts of use.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cpl-3
+</t>
+  </si>
+  <si>
+    <t>{Request that resulted in Event in activity.actionResulting}</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail</t>
+  </si>
+  <si>
+    <t>In-line definition of activity</t>
+  </si>
+  <si>
+    <t>A simple summary of a planned activity suitable for a general care plan system (e.g. form driven) that doesn't know about specific resources such as procedure etc.</t>
+  </si>
+  <si>
+    <t>Details in a simple form for generic care plan systems.</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COMP, subsetCode=SUMM].target</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.id</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.extension</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.modifierExtension</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.kind</t>
+  </si>
+  <si>
+    <t>Appointment | CommunicationRequest | DeviceRequest | MedicationRequest | NutritionOrder | Task | ServiceRequest | VisionPrescription</t>
+  </si>
+  <si>
+    <t>A description of the kind of resource the in-line definition of a care plan activity is representing.  The CarePlan.activity.detail is an in-line definition when a resource is not referenced using CarePlan.activity.reference.  For example, a MedicationRequest, a ServiceRequest, or a CommunicationRequest.</t>
+  </si>
+  <si>
+    <t>May determine what types of extensions are permitted.</t>
+  </si>
+  <si>
+    <t>Resource types defined as part of FHIR that can be represented as in-line definitions of a care plan activity.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-kind|4.0.1</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=COMP].source[classCode=LIST].code</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>The URL pointing to a FHIR-defined protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan activity.</t>
+  </si>
+  <si>
+    <t>Allows Questionnaires that the patient (or practitioner) should fill in to fulfill the care plan activity.</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.instantiatesUri</t>
+  </si>
+  <si>
+    <t>The URL pointing to an externally maintained protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan activity.</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.code</t>
+  </si>
+  <si>
+    <t>Detail type of activity</t>
+  </si>
+  <si>
+    <t>Detailed description of the type of planned activity; e.g. what lab test, what procedure, what kind of encounter.</t>
+  </si>
+  <si>
+    <t>Tends to be less relevant for activities involving particular products.  Codes should not convey negation - use "prohibited" instead.</t>
+  </si>
+  <si>
+    <t>Allows matching performed to planned as well as validation against protocols.</t>
+  </si>
+  <si>
+    <t>Detailed description of the type of activity; e.g. What lab test, what procedure, what kind of encounter.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
+  </si>
+  <si>
+    <t>Request.code</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>OBR-4 / RXE-2 / RXO-1 / RXD-2</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.reasonCode</t>
+  </si>
+  <si>
+    <t>Why activity should be done or why activity was prohibited</t>
+  </si>
+  <si>
+    <t>Provides the rationale that drove the inclusion of this particular activity as part of the plan or the reason why the activity was prohibited.</t>
+  </si>
+  <si>
+    <t>This could be a diagnosis code.  If a full condition record exists or additional detail is needed, use reasonCondition instead.</t>
+  </si>
+  <si>
+    <t>Identifies why a care plan activity is needed.  Can include any health condition codes as well as such concepts as "general wellness", prophylaxis, surgical preparation, etc.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
+  </si>
+  <si>
+    <t>Request.reasonCode</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.reasonReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Why activity is needed</t>
+  </si>
+  <si>
+    <t>Indicates another resource, such as the health condition(s), whose existence justifies this request and drove the inclusion of this particular activity as part of the plan.</t>
+  </si>
+  <si>
+    <t>Conditions can be identified at the activity level that are not identified as reasons for the overall plan.</t>
+  </si>
+  <si>
+    <t>CarePlan.activity.detail.goal</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reference(Goal|4.0.1)
 </t>
-  </si>
-  <si>
-    <t>Desired outcome of plan</t>
-  </si>
-  <si>
-    <t>Describes the intended objective(s) of carrying out the care plan.</t>
-  </si>
-  <si>
-    <t>Goal can be achieving a particular change or merely maintaining a current state or even slowing a decline.</t>
-  </si>
-  <si>
-    <t>Provides context for plan.  Allows plan effectiveness to be evaluated by clinicians.</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode&lt;=OBJ].</t>
-  </si>
-  <si>
-    <t>GOL.1</t>
-  </si>
-  <si>
-    <t>CarePlan.activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Diagnostische Maßnahmen</t>
-  </si>
-  <si>
-    <t>Geplante bzw. durchgeführte Schritte des Diagnosepfads.</t>
-  </si>
-  <si>
-    <t>Allows systems to prompt for performance of planned activities, and validate plans against best practice.</t>
-  </si>
-  <si>
-    <t>cpl-3:Provide a reference or detail, not both {detail.empty() or reference.empty()}
-ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
-  </si>
-  <si>
-    <t>{no mapping
-NOTE: This is a list of contained Request-Event tuples!}</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP].target</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.id</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.outcomeCodeableConcept</t>
-  </si>
-  <si>
-    <t>Results of the activity</t>
-  </si>
-  <si>
-    <t>Identifies the outcome at the point when the status of the activity is assessed.  For example, the outcome of an education activity could be patient understands (or not).</t>
-  </si>
-  <si>
-    <t>Note that this should not duplicate the activity status (e.g. completed or in progress).</t>
-  </si>
-  <si>
-    <t>Identifies the results of the activity.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome|4.0.1</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.outcomeReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(DiagnosticReport|Observation|Procedure)
-</t>
-  </si>
-  <si>
-    <t>Ergebnis</t>
-  </si>
-  <si>
-    <t>Referenz auf das Ergebnis der Diagnostik – z. B. DiagnosticReport oder Observation.</t>
-  </si>
-  <si>
-    <t>The activity outcome is independent of the outcome of the related goal(s).  For example, if the goal is to achieve a target body weight of 150 lbs and an activity is defined to diet, then the activity outcome could be calories consumed whereas the goal outcome is an observation for the actual body weight measured.</t>
-  </si>
-  <si>
-    <t>Links plan to resulting actions.</t>
-  </si>
-  <si>
-    <t>{Event that is outcome of Request in activity.reference}</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=FLFS].source</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annotation
-</t>
-  </si>
-  <si>
-    <t>Comments about the activity status/progress</t>
-  </si>
-  <si>
-    <t>Notes about the adherence/status/progress of the activity.</t>
-  </si>
-  <si>
-    <t>This element should NOT be used to describe the activity to be performed - that occurs either within the resource pointed to by activity.detail.reference or in activity.detail.description.</t>
-  </si>
-  <si>
-    <t>Can be used to capture information about adherence, progress, concerns, etc.</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="annotation"].value</t>
-  </si>
-  <si>
-    <t>NTE?</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(ServiceRequest|Appointment|Task)
-</t>
-  </si>
-  <si>
-    <t>Geplante Maßnahme</t>
-  </si>
-  <si>
-    <t>Referenz auf eine geplante diagnostische Maßnahme – z. B. ServiceRequest.</t>
-  </si>
-  <si>
-    <t>Standard extension exists ([resource-pertainsToGoal](http://hl7.org/fhir/R4/extension-resource-pertainstogoal.html)) that allows goals to be referenced from any of the referenced resources in CarePlan.activity.reference.  -The goal should be visible when the resource referenced by CarePlan.activity.reference is viewed independently from the CarePlan.  Requests that are pointed to by a CarePlan using this element should *not* point to this CarePlan using the "basedOn" element.  i.e. Requests that are part of a CarePlan are not "based on" the CarePlan.</t>
-  </si>
-  <si>
-    <t>Details in a form consistent with other applications and contexts of use.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cpl-3
-</t>
-  </si>
-  <si>
-    <t>{Request that resulted in Event in activity.actionResulting}</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail</t>
-  </si>
-  <si>
-    <t>In-line definition of activity</t>
-  </si>
-  <si>
-    <t>A simple summary of a planned activity suitable for a general care plan system (e.g. form driven) that doesn't know about specific resources such as procedure etc.</t>
-  </si>
-  <si>
-    <t>Details in a simple form for generic care plan systems.</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COMP, subsetCode=SUMM].target</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.id</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.extension</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.modifierExtension</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.kind</t>
-  </si>
-  <si>
-    <t>Appointment | CommunicationRequest | DeviceRequest | MedicationRequest | NutritionOrder | Task | ServiceRequest | VisionPrescription</t>
-  </si>
-  <si>
-    <t>A description of the kind of resource the in-line definition of a care plan activity is representing.  The CarePlan.activity.detail is an in-line definition when a resource is not referenced using CarePlan.activity.reference.  For example, a MedicationRequest, a ServiceRequest, or a CommunicationRequest.</t>
-  </si>
-  <si>
-    <t>May determine what types of extensions are permitted.</t>
-  </si>
-  <si>
-    <t>Resource types defined as part of FHIR that can be represented as in-line definitions of a care plan activity.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-kind|4.0.1</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=COMP].source[classCode=LIST].code</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.instantiatesCanonical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>The URL pointing to a FHIR-defined protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan activity.</t>
-  </si>
-  <si>
-    <t>Allows Questionnaires that the patient (or practitioner) should fill in to fulfill the care plan activity.</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.instantiatesUri</t>
-  </si>
-  <si>
-    <t>The URL pointing to an externally maintained protocol, guideline, questionnaire or other definition that is adhered to in whole or in part by this CarePlan activity.</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.code</t>
-  </si>
-  <si>
-    <t>Detail type of activity</t>
-  </si>
-  <si>
-    <t>Detailed description of the type of planned activity; e.g. what lab test, what procedure, what kind of encounter.</t>
-  </si>
-  <si>
-    <t>Tends to be less relevant for activities involving particular products.  Codes should not convey negation - use "prohibited" instead.</t>
-  </si>
-  <si>
-    <t>Allows matching performed to planned as well as validation against protocols.</t>
-  </si>
-  <si>
-    <t>Detailed description of the type of activity; e.g. What lab test, what procedure, what kind of encounter.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.code</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>OBR-4 / RXE-2 / RXO-1 / RXD-2</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.reasonCode</t>
-  </si>
-  <si>
-    <t>Why activity should be done or why activity was prohibited</t>
-  </si>
-  <si>
-    <t>Provides the rationale that drove the inclusion of this particular activity as part of the plan or the reason why the activity was prohibited.</t>
-  </si>
-  <si>
-    <t>This could be a diagnosis code.  If a full condition record exists or additional detail is needed, use reasonCondition instead.</t>
-  </si>
-  <si>
-    <t>Identifies why a care plan activity is needed.  Can include any health condition codes as well as such concepts as "general wellness", prophylaxis, surgical preparation, etc.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.reasonCode</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.reasonReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Why activity is needed</t>
-  </si>
-  <si>
-    <t>Indicates another resource, such as the health condition(s), whose existence justifies this request and drove the inclusion of this particular activity as part of the plan.</t>
-  </si>
-  <si>
-    <t>Conditions can be identified at the activity level that are not identified as reasons for the overall plan.</t>
-  </si>
-  <si>
-    <t>CarePlan.activity.detail.goal</t>
   </si>
   <si>
     <t>Goals this activity relates to</t>
@@ -4023,7 +4027,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>203</v>
       </c>
@@ -4042,7 +4046,7 @@
         <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>89</v>
@@ -5967,7 +5971,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>330</v>
       </c>
@@ -5986,7 +5990,7 @@
         <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>80</v>
@@ -8173,17 +8177,17 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>331</v>
+        <v>427</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8261,10 +8265,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8290,16 +8294,16 @@
         <v>108</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -8327,10 +8331,10 @@
         <v>196</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8348,7 +8352,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>88</v>
@@ -8363,24 +8367,24 @@
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8406,13 +8410,13 @@
         <v>212</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8462,7 +8466,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8477,7 +8481,7 @@
         <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>80</v>
@@ -8491,10 +8495,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8517,70 +8521,70 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q58" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="R58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF58" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="P58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q58" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="R58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8595,10 +8599,10 @@
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>80</v>
@@ -8609,10 +8613,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8635,17 +8639,17 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -8694,7 +8698,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8718,15 +8722,15 @@
         <v>80</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8749,19 +8753,19 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>80</v>
@@ -8810,7 +8814,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8828,21 +8832,21 @@
         <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8865,19 +8869,19 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>80</v>
@@ -8926,7 +8930,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8941,24 +8945,24 @@
         <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8981,13 +8985,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9017,10 +9021,10 @@
         <v>217</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -9038,7 +9042,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9056,25 +9060,25 @@
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9093,17 +9097,17 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -9152,7 +9156,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9170,21 +9174,21 @@
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9207,13 +9211,13 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9264,7 +9268,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9282,21 +9286,21 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9322,10 +9326,10 @@
         <v>222</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9376,7 +9380,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9394,7 +9398,7 @@
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>80</v>
@@ -9405,10 +9409,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9434,14 +9438,14 @@
         <v>368</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -9490,7 +9494,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9505,7 +9509,7 @@
         <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>373</v>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:21:47+00:00</t>
+    <t>2026-07-31T12:58:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:58:15+00:00</t>
+    <t>2026-07-31T13:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:16:40+00:00</t>
+    <t>2026-07-31T13:26:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:26:52+00:00</t>
+    <t>2026-07-31T13:33:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:33:02+00:00</t>
+    <t>2026-07-31T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:38:59+00:00</t>
+    <t>2026-07-31T13:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:45:11+00:00</t>
+    <t>2026-07-31T14:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:14:54+00:00</t>
+    <t>2026-07-31T14:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:25:45+00:00</t>
+    <t>2026-08-02T18:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:42:01+00:00</t>
+    <t>2026-08-02T18:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
+++ b/ci-build/StructureDefinition-onko-diagnostic-care-plan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:51:55+00:00</t>
+    <t>2026-08-03T05:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
